--- a/outputs/ranker/baseline/candidate_feature_matrix.xlsx
+++ b/outputs/ranker/baseline/candidate_feature_matrix.xlsx
@@ -172,19 +172,19 @@
     <t>OPTIMAL</t>
   </si>
   <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_01_min_unserved.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_02_fairness.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_03_vehicle_preservation.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_04_fatigue.xlsx</t>
-  </si>
-  <si>
-    <t>/mnt/data/work_v05/G-LIFT_v.0.4.0_optimizer_stabilized_ranker_spec/outputs/candidates/baseline/candidate_05_expert_style.xlsx</t>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_01_min_unserved.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_02_fairness.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_03_vehicle_preservation.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_04_fatigue.xlsx</t>
+  </si>
+  <si>
+    <t>/home/hk416an/dev/Bus/outputs/candidates/baseline/candidate_05_expert_style.xlsx</t>
   </si>
 </sst>
 </file>
@@ -708,13 +708,13 @@
         <v>85</v>
       </c>
       <c r="N2">
-        <v>46.531</v>
+        <v>49.854</v>
       </c>
       <c r="O2">
         <v>55</v>
       </c>
       <c r="P2">
-        <v>60.072</v>
+        <v>63.606</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -747,16 +747,16 @@
         <v>540</v>
       </c>
       <c r="AA2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB2">
-        <v>17.647</v>
+        <v>23.529</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD2">
-        <v>3.571</v>
+        <v>7.143</v>
       </c>
       <c r="AE2">
         <v>5</v>
@@ -771,13 +771,13 @@
         <v>100</v>
       </c>
       <c r="AI2">
-        <v>43.736</v>
+        <v>46.688</v>
       </c>
       <c r="AJ2">
-        <v>17.647</v>
+        <v>23.529</v>
       </c>
       <c r="AK2">
-        <v>3.571</v>
+        <v>7.143</v>
       </c>
       <c r="AL2">
         <v>83.333</v>
@@ -786,7 +786,7 @@
         <v>52</v>
       </c>
       <c r="AN2">
-        <v>76.05423999999999</v>
+        <v>76.50287</v>
       </c>
     </row>
     <row r="3" spans="1:40">
@@ -854,7 +854,7 @@
         <v>100</v>
       </c>
       <c r="V3">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="W3">
         <v>100</v>
@@ -908,7 +908,7 @@
         <v>53</v>
       </c>
       <c r="AN3">
-        <v>75.71343999999999</v>
+        <v>75.23186</v>
       </c>
     </row>
     <row r="4" spans="1:40">
@@ -952,13 +952,13 @@
         <v>85</v>
       </c>
       <c r="N4">
-        <v>41.057</v>
+        <v>46.531</v>
       </c>
       <c r="O4">
         <v>55</v>
       </c>
       <c r="P4">
-        <v>54.065</v>
+        <v>60.072</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -976,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="W4">
         <v>100</v>
@@ -997,10 +997,10 @@
         <v>29.412</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="AE4">
         <v>5</v>
@@ -1015,13 +1015,13 @@
         <v>100</v>
       </c>
       <c r="AI4">
-        <v>46.961</v>
+        <v>47.854</v>
       </c>
       <c r="AJ4">
         <v>29.412</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="AL4">
         <v>83.333</v>
@@ -1030,7 +1030,7 @@
         <v>54</v>
       </c>
       <c r="AN4">
-        <v>75.14403999999999</v>
+        <v>75.72197</v>
       </c>
     </row>
     <row r="5" spans="1:40">
@@ -1113,10 +1113,10 @@
         <v>540</v>
       </c>
       <c r="AA5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB5">
-        <v>38.235</v>
+        <v>35.294</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>100</v>
       </c>
       <c r="AI5">
-        <v>50.049</v>
+        <v>49.02</v>
       </c>
       <c r="AJ5">
-        <v>38.235</v>
+        <v>35.294</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>55</v>
       </c>
       <c r="AN5">
-        <v>76.09411999999999</v>
+        <v>75.5758</v>
       </c>
     </row>
     <row r="6" spans="1:40">
@@ -1196,7 +1196,7 @@
         <v>82.10299999999999</v>
       </c>
       <c r="N6">
-        <v>46.531</v>
+        <v>49.854</v>
       </c>
       <c r="O6">
         <v>55</v>
@@ -1220,7 +1220,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="W6">
         <v>100</v>
@@ -1274,7 +1274,7 @@
         <v>56</v>
       </c>
       <c r="AN6">
-        <v>82.57122999999999</v>
+        <v>83.85393999999999</v>
       </c>
     </row>
   </sheetData>
